--- a/リフレッシュトークン手動更新手順.xlsx
+++ b/リフレッシュトークン手動更新手順.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai-script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B536EB8-7804-42B9-8B45-0E5E03829AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E545B3B-D408-4570-9625-5DE8B0B7E0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5B81C77D-DAD5-4159-B073-E03E292F3C5F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="リフレッシュトークン更新手順" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,18 +34,190 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>ここに手動の更新の仕方をかく</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+  <si>
+    <t>1.認可URLを作ってアクセスする</t>
+    <rPh sb="2" eb="4">
+      <t>ニンカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のクライアントIDを入力→</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>52220540834-2qmrh47s2kv595v13ka7dqtqjt2ndck0.apps.googleusercontent.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認可URL↓</t>
+    <rPh sb="0" eb="2">
+      <t>ニンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のクライアントIDを入力すると自動で認可URLが作成されます。</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ニンカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（※クライアンドIDはメモしているものか、mykey.jsonに記載があります。）</t>
+    <rPh sb="32" eb="34">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>http://localhost/?code=4/0ATX87lNdBy2sjOWjjq5VPylsN9fm4OMmlqyY9qrRjn14Dpx3TMKn-P4C5e9a3amu6_jgwQ&amp;scope=https://www.googleapis.com/auth/youtube.force-ssl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下記にURLをペーストしてください</t>
+    <rPh sb="0" eb="2">
+      <t>カキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.許可しているアカウントを指定して、アクセスキーコードを取得</t>
+    <rPh sb="2" eb="4">
+      <t>キョカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセスキーコード自動抽出結果：</t>
+    <rPh sb="9" eb="13">
+      <t>ジドウチュウシュツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３.コマンドプロンプトでアクセスキーコードなどの情報を使って、アクセクトークンを取得</t>
+    <rPh sb="24" eb="26">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【コマンドプロンプト】</t>
+  </si>
+  <si>
+    <t>curl -X POST "https://oauth2.googleapis.com/token" ^</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --data-urlencode "client_id=52220540834-2qmrh47s2kv595v13ka7dqtqjt2ndck0.apps.googleusercontent.com" ^</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --data-urlencode "client_secret=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" ^</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --data-urlencode "redirect_uri=http://localhost" ^</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --data-urlencode "grant_type=authorization_code"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --data-urlencode "code=4/0Ab32j90MZjv6IpAFGji_6AvcHwmEIC3sp1A59eTM-2u6oGFrGLTDxXlIqzICiLdYj0PYaA" ^</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←自分のクライアントIDを使ってください</t>
+    <rPh sb="1" eb="3">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←自分のシークレットコードを使ってください　※クライアントIDとセット</t>
+    <rPh sb="1" eb="3">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←上記アクセスキーコードを使用してください</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上記の情報を書き換えたら、コマンドプロンプトに張り付けて実行してください。</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウキ</t>
+    </rPh>
     <rPh sb="3" eb="5">
-      <t>シュドウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シカタ</t>
-    </rPh>
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  --data-urlencode "grant_type=authorization_code"</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -53,7 +225,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,16 +241,38 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -86,18 +280,190 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -111,6 +477,455 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>363639</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38706</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14E1A667-6008-480B-AD85-C2E05A12C639}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="662940" y="2971800"/>
+          <a:ext cx="5676049" cy="3010506"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>211194</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>149311</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE41BF04-6BB0-4B14-A6F8-AAF9AD6085ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="662940" y="6172200"/>
+          <a:ext cx="9496164" cy="3349711"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>364372</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>227901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B209641-D16E-440D-9B9A-03DF48C4BEB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="662940" y="9829800"/>
+          <a:ext cx="8986402" cy="5257101"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>341468</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>60428</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43CFDAD9-0D4C-4603-B5F9-EEB63A841D28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="662940" y="15316200"/>
+          <a:ext cx="11611448" cy="6915888"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219710</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>10160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>626110</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="吹き出し: 四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0605557-3699-0ECD-8150-493C703087E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6849110" y="4582160"/>
+          <a:ext cx="2395220" cy="546100"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -60917"/>
+            <a:gd name="adj2" fmla="val 13682"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>許可しているアカウントを選択</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>212090</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>93980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="吹き出し: 四角形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5016DDC-3D4C-4D9E-886F-DFEF717FCB30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8412480" y="8923020"/>
+          <a:ext cx="2406650" cy="543560"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -60917"/>
+            <a:gd name="adj2" fmla="val 13682"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>続行をクリック</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="吹き出し: 四角形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B0ACB81-86F0-4EE8-A136-F8DB9FEF86A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9662160" y="14333220"/>
+          <a:ext cx="2407920" cy="551180"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -60917"/>
+            <a:gd name="adj2" fmla="val 13682"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>続行をクリック</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>568960</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>367030</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="吹き出し: 四角形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0A6C7EA-B546-4A75-831B-65BF79A5DF6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12501880" y="15430500"/>
+          <a:ext cx="2449830" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -60917"/>
+            <a:gd name="adj2" fmla="val 13682"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>URL</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>に返ってきたコードを使用します。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -410,16 +1225,336 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171FAAD8-FD6C-481B-9862-C6787CEA2737}">
-  <dimension ref="A2"/>
+  <dimension ref="A1:S124"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="4"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="1" t="str">
+        <f>"https://accounts.google.com/o/oauth2/auth?client_id=" &amp; F4 &amp; "&amp;redirect_uri=http://localhost&amp;
+response_type=code&amp;
+scope=https://www.googleapis.com/auth/youtube.force-ssl&amp;
+access_type=offline&amp;
+prompt=consent"</f>
+        <v>https://accounts.google.com/o/oauth2/auth?client_id=52220540834-2qmrh47s2kv595v13ka7dqtqjt2ndck0.apps.googleusercontent.com&amp;redirect_uri=http://localhost&amp;
+response_type=code&amp;
+scope=https://www.googleapis.com/auth/youtube.force-ssl&amp;
+access_type=offline&amp;
+prompt=consent</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
+      <c r="M101" s="7"/>
+      <c r="N101" s="7"/>
+      <c r="O101" s="7"/>
+      <c r="P101" s="7"/>
+      <c r="Q101" s="7"/>
+      <c r="R101" s="7"/>
+      <c r="S101" s="8"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" t="str">
+        <f>RIGHT(LEFT(B101,FIND("&amp;scope",B101)-1),LEN(LEFT(B101,FIND("&amp;scope",B101)-1))-FIND("code=",LEFT(B101,FIND("&amp;scope",B101)-1))-4)</f>
+        <v>4/0ATX87lNdBy2sjOWjjq5VPylsN9fm4OMmlqyY9qrRjn14Dpx3TMKn-P4C5e9a3amu6_jgwQ</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="10"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="10"/>
+      <c r="F110" s="10"/>
+      <c r="G110" s="10"/>
+      <c r="H110" s="10"/>
+      <c r="I110" s="10"/>
+      <c r="J110" s="10"/>
+      <c r="K110" s="10"/>
+      <c r="L110" s="10"/>
+      <c r="M110" s="11"/>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" s="13"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="13"/>
+      <c r="J111" s="13"/>
+      <c r="K111" s="13"/>
+      <c r="L111" s="13"/>
+      <c r="M111" s="14"/>
+      <c r="N111" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="13"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
+      <c r="K112" s="13"/>
+      <c r="L112" s="13"/>
+      <c r="M112" s="14"/>
+      <c r="N112" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
+      <c r="I113" s="13"/>
+      <c r="J113" s="13"/>
+      <c r="K113" s="13"/>
+      <c r="L113" s="13"/>
+      <c r="M113" s="14"/>
+      <c r="N113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" s="13"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
+      <c r="I114" s="13"/>
+      <c r="J114" s="13"/>
+      <c r="K114" s="13"/>
+      <c r="L114" s="13"/>
+      <c r="M114" s="14"/>
+    </row>
+    <row r="115" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="16"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="16"/>
+      <c r="H115" s="16"/>
+      <c r="I115" s="16"/>
+      <c r="J115" s="16"/>
+      <c r="K115" s="16"/>
+      <c r="L115" s="16"/>
+      <c r="M115" s="17"/>
+    </row>
+    <row r="117" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" s="9" t="str">
+        <f>"curl -X POST ""https://oauth2.googleapis.com/token"" ^"</f>
+        <v>curl -X POST "https://oauth2.googleapis.com/token" ^</v>
+      </c>
+      <c r="C119" s="10"/>
+      <c r="D119" s="10"/>
+      <c r="E119" s="10"/>
+      <c r="F119" s="10"/>
+      <c r="G119" s="10"/>
+      <c r="H119" s="10"/>
+      <c r="I119" s="10"/>
+      <c r="J119" s="10"/>
+      <c r="K119" s="10"/>
+      <c r="L119" s="10"/>
+      <c r="M119" s="11"/>
+    </row>
+    <row r="120" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" s="12" t="str">
+        <f>"  --data-urlencode ""code=" &amp; B104 &amp; """ ^"</f>
+        <v xml:space="preserve">  --data-urlencode "code=4/0ATX87lNdBy2sjOWjjq5VPylsN9fm4OMmlqyY9qrRjn14Dpx3TMKn-P4C5e9a3amu6_jgwQ" ^</v>
+      </c>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
+      <c r="I120" s="13"/>
+      <c r="J120" s="13"/>
+      <c r="K120" s="13"/>
+      <c r="L120" s="13"/>
+      <c r="M120" s="14"/>
+    </row>
+    <row r="121" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C121" s="13"/>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="13"/>
+      <c r="J121" s="13"/>
+      <c r="K121" s="13"/>
+      <c r="L121" s="13"/>
+      <c r="M121" s="14"/>
+    </row>
+    <row r="122" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="13"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="13"/>
+      <c r="K122" s="13"/>
+      <c r="L122" s="13"/>
+      <c r="M122" s="14"/>
+    </row>
+    <row r="123" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" s="13"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="13"/>
+      <c r="H123" s="13"/>
+      <c r="I123" s="13"/>
+      <c r="J123" s="13"/>
+      <c r="K123" s="13"/>
+      <c r="L123" s="13"/>
+      <c r="M123" s="14"/>
+    </row>
+    <row r="124" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C124" s="16"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="16"/>
+      <c r="F124" s="16"/>
+      <c r="G124" s="16"/>
+      <c r="H124" s="16"/>
+      <c r="I124" s="16"/>
+      <c r="J124" s="16"/>
+      <c r="K124" s="16"/>
+      <c r="L124" s="16"/>
+      <c r="M124" s="17"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F4:Q4"/>
+    <mergeCell ref="B101:S101"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" display="https://accounts.google.com/o/oauth2/auth?client_id=52220540834-2qmrh47s2kv595v13ka7dqtqjt2ndck0.apps.googleusercontent.com&amp;redirect_uri=http://localhost&amp;_x000a_response_type=code&amp;_x000a_scope=https://www.googleapis.com/auth/youtube.force-ssl&amp;_x000a_access_type=offline&amp;_x000a_prompt=consent" xr:uid="{81AA84C6-FCB8-4625-9929-31A7813ED4B4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/リフレッシュトークン手動更新手順.xlsx
+++ b/リフレッシュトークン手動更新手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai-script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E545B3B-D408-4570-9625-5DE8B0B7E0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86173D2-AF8A-4985-9BB8-A6BCF5152ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5B81C77D-DAD5-4159-B073-E03E292F3C5F}"/>
   </bookViews>
@@ -406,13 +406,43 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -421,45 +451,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1234,7 +1225,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1245,20 +1236,20 @@
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="4"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
@@ -1295,26 +1286,26 @@
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="7"/>
-      <c r="K101" s="7"/>
-      <c r="L101" s="7"/>
-      <c r="M101" s="7"/>
-      <c r="N101" s="7"/>
-      <c r="O101" s="7"/>
-      <c r="P101" s="7"/>
-      <c r="Q101" s="7"/>
-      <c r="R101" s="7"/>
-      <c r="S101" s="8"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
+      <c r="J101" s="13"/>
+      <c r="K101" s="13"/>
+      <c r="L101" s="13"/>
+      <c r="M101" s="13"/>
+      <c r="N101" s="13"/>
+      <c r="O101" s="13"/>
+      <c r="P101" s="13"/>
+      <c r="Q101" s="13"/>
+      <c r="R101" s="13"/>
+      <c r="S101" s="14"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" t="s">
@@ -1338,109 +1329,109 @@
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="9" t="s">
+      <c r="B110" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="11"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="5"/>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C111" s="13"/>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="13"/>
-      <c r="H111" s="13"/>
-      <c r="I111" s="13"/>
-      <c r="J111" s="13"/>
-      <c r="K111" s="13"/>
-      <c r="L111" s="13"/>
-      <c r="M111" s="14"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="7"/>
+      <c r="M111" s="8"/>
       <c r="N111" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="13"/>
-      <c r="H112" s="13"/>
-      <c r="I112" s="13"/>
-      <c r="J112" s="13"/>
-      <c r="K112" s="13"/>
-      <c r="L112" s="13"/>
-      <c r="M112" s="14"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="7"/>
+      <c r="K112" s="7"/>
+      <c r="L112" s="7"/>
+      <c r="M112" s="8"/>
       <c r="N112" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="113" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C113" s="13"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="13"/>
-      <c r="J113" s="13"/>
-      <c r="K113" s="13"/>
-      <c r="L113" s="13"/>
-      <c r="M113" s="14"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+      <c r="M113" s="8"/>
       <c r="N113" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="114" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C114" s="13"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="13"/>
-      <c r="H114" s="13"/>
-      <c r="I114" s="13"/>
-      <c r="J114" s="13"/>
-      <c r="K114" s="13"/>
-      <c r="L114" s="13"/>
-      <c r="M114" s="14"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="7"/>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7"/>
+      <c r="M114" s="8"/>
     </row>
     <row r="115" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="15" t="s">
+      <c r="B115" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
-      <c r="F115" s="16"/>
-      <c r="G115" s="16"/>
-      <c r="H115" s="16"/>
-      <c r="I115" s="16"/>
-      <c r="J115" s="16"/>
-      <c r="K115" s="16"/>
-      <c r="L115" s="16"/>
-      <c r="M115" s="17"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="10"/>
+      <c r="E115" s="10"/>
+      <c r="F115" s="10"/>
+      <c r="G115" s="10"/>
+      <c r="H115" s="10"/>
+      <c r="I115" s="10"/>
+      <c r="J115" s="10"/>
+      <c r="K115" s="10"/>
+      <c r="L115" s="10"/>
+      <c r="M115" s="11"/>
     </row>
     <row r="117" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" t="s">
@@ -1448,102 +1439,102 @@
       </c>
     </row>
     <row r="119" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B119" s="9" t="str">
+      <c r="B119" s="3" t="str">
         <f>"curl -X POST ""https://oauth2.googleapis.com/token"" ^"</f>
         <v>curl -X POST "https://oauth2.googleapis.com/token" ^</v>
       </c>
-      <c r="C119" s="10"/>
-      <c r="D119" s="10"/>
-      <c r="E119" s="10"/>
-      <c r="F119" s="10"/>
-      <c r="G119" s="10"/>
-      <c r="H119" s="10"/>
-      <c r="I119" s="10"/>
-      <c r="J119" s="10"/>
-      <c r="K119" s="10"/>
-      <c r="L119" s="10"/>
-      <c r="M119" s="11"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="5"/>
     </row>
     <row r="120" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="12" t="str">
+      <c r="B120" s="6" t="str">
         <f>"  --data-urlencode ""code=" &amp; B104 &amp; """ ^"</f>
         <v xml:space="preserve">  --data-urlencode "code=4/0ATX87lNdBy2sjOWjjq5VPylsN9fm4OMmlqyY9qrRjn14Dpx3TMKn-P4C5e9a3amu6_jgwQ" ^</v>
       </c>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="13"/>
-      <c r="J120" s="13"/>
-      <c r="K120" s="13"/>
-      <c r="L120" s="13"/>
-      <c r="M120" s="14"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="7"/>
+      <c r="J120" s="7"/>
+      <c r="K120" s="7"/>
+      <c r="L120" s="7"/>
+      <c r="M120" s="8"/>
     </row>
     <row r="121" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="12" t="s">
+      <c r="B121" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C121" s="13"/>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13"/>
-      <c r="F121" s="13"/>
-      <c r="G121" s="13"/>
-      <c r="H121" s="13"/>
-      <c r="I121" s="13"/>
-      <c r="J121" s="13"/>
-      <c r="K121" s="13"/>
-      <c r="L121" s="13"/>
-      <c r="M121" s="14"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7"/>
+      <c r="J121" s="7"/>
+      <c r="K121" s="7"/>
+      <c r="L121" s="7"/>
+      <c r="M121" s="8"/>
     </row>
     <row r="122" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B122" s="12" t="s">
+      <c r="B122" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C122" s="13"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="13"/>
-      <c r="J122" s="13"/>
-      <c r="K122" s="13"/>
-      <c r="L122" s="13"/>
-      <c r="M122" s="14"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="7"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="7"/>
+      <c r="K122" s="7"/>
+      <c r="L122" s="7"/>
+      <c r="M122" s="8"/>
     </row>
     <row r="123" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C123" s="13"/>
-      <c r="D123" s="13"/>
-      <c r="E123" s="13"/>
-      <c r="F123" s="13"/>
-      <c r="G123" s="13"/>
-      <c r="H123" s="13"/>
-      <c r="I123" s="13"/>
-      <c r="J123" s="13"/>
-      <c r="K123" s="13"/>
-      <c r="L123" s="13"/>
-      <c r="M123" s="14"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="7"/>
+      <c r="J123" s="7"/>
+      <c r="K123" s="7"/>
+      <c r="L123" s="7"/>
+      <c r="M123" s="8"/>
     </row>
     <row r="124" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="15" t="s">
+      <c r="B124" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C124" s="16"/>
-      <c r="D124" s="16"/>
-      <c r="E124" s="16"/>
-      <c r="F124" s="16"/>
-      <c r="G124" s="16"/>
-      <c r="H124" s="16"/>
-      <c r="I124" s="16"/>
-      <c r="J124" s="16"/>
-      <c r="K124" s="16"/>
-      <c r="L124" s="16"/>
-      <c r="M124" s="17"/>
+      <c r="C124" s="10"/>
+      <c r="D124" s="10"/>
+      <c r="E124" s="10"/>
+      <c r="F124" s="10"/>
+      <c r="G124" s="10"/>
+      <c r="H124" s="10"/>
+      <c r="I124" s="10"/>
+      <c r="J124" s="10"/>
+      <c r="K124" s="10"/>
+      <c r="L124" s="10"/>
+      <c r="M124" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/リフレッシュトークン手動更新手順.xlsx
+++ b/リフレッシュトークン手動更新手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai-script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86173D2-AF8A-4985-9BB8-A6BCF5152ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C5EEF1-AE37-4CC0-A554-B09721DD6757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5B81C77D-DAD5-4159-B073-E03E292F3C5F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>1.認可URLを作ってアクセスする</t>
     <rPh sb="2" eb="4">
@@ -93,17 +93,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>http://localhost/?code=4/0ATX87lNdBy2sjOWjjq5VPylsN9fm4OMmlqyY9qrRjn14Dpx3TMKn-P4C5e9a3amu6_jgwQ&amp;scope=https://www.googleapis.com/auth/youtube.force-ssl</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>下記にURLをペーストしてください</t>
-    <rPh sb="0" eb="2">
-      <t>カキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2.許可しているアカウントを指定して、アクセスキーコードを取得</t>
     <rPh sb="2" eb="4">
       <t>キョカ</t>
@@ -146,50 +135,10 @@
     <t>curl -X POST "https://oauth2.googleapis.com/token" ^</t>
   </si>
   <si>
-    <t xml:space="preserve">  --data-urlencode "client_id=52220540834-2qmrh47s2kv595v13ka7dqtqjt2ndck0.apps.googleusercontent.com" ^</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  --data-urlencode "client_secret=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" ^</t>
-  </si>
-  <si>
     <t xml:space="preserve">  --data-urlencode "redirect_uri=http://localhost" ^</t>
   </si>
   <si>
     <t xml:space="preserve">  --data-urlencode "grant_type=authorization_code"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  --data-urlencode "code=4/0Ab32j90MZjv6IpAFGji_6AvcHwmEIC3sp1A59eTM-2u6oGFrGLTDxXlIqzICiLdYj0PYaA" ^</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>←自分のクライアントIDを使ってください</t>
-    <rPh sb="1" eb="3">
-      <t>ジブン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>←自分のシークレットコードを使ってください　※クライアントIDとセット</t>
-    <rPh sb="1" eb="3">
-      <t>ジブン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>←上記アクセスキーコードを使用してください</t>
-    <rPh sb="1" eb="3">
-      <t>ジョウキ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>上記の情報を書き換えたら、コマンドプロンプトに張り付けて実行してください。</t>
@@ -217,7 +166,163 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">  --data-urlencode "grant_type=authorization_code"</t>
+    <t>←上のアクセスキーコード自動抽出結果が自動反映されます</t>
+    <rPh sb="1" eb="2">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>チュウシュツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←自分のクライアントIDを使って赤字を書き換えてください</t>
+    <rPh sb="1" eb="3">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>アカジ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  --data-urlencode "client_id=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>52220540834-2qmrh47s2kv595v13ka7dqtqjt2ndck0.apps.googleusercontent.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" ^</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  --data-urlencode "client_secret=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>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</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" ^</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←自分のシークレットコードを使って赤字を書き換えてください　※クライアントIDとセット</t>
+    <rPh sb="1" eb="3">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>http://localhost/?code=4/0ATX87lPXgQMsyNd5hcMYeNlwFU5igZ77FB8fUD1UVsVA33oWE3gmpg_QTrqA34mQGpc71g&amp;scope=https://www.googleapis.com/auth/youtube.force-ssl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑アクセストークンとリフレッシュトークンが返却されれば成功</t>
+    <rPh sb="21" eb="23">
+      <t>ヘンキャク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C:\ai-script\configにある「youtube_tokens.json」ファイルのaccess_tokenとrefresh_tokenを書き換える。</t>
+    <rPh sb="75" eb="76">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これでリフレッシュトークンの完了！！</t>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下記に取得したURLをペーストしてください（セルをダブルクリックするなど、セルの編集モードで記載すること）URLそのままペーストはうまく張り付けできないことも</t>
+    <rPh sb="0" eb="2">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -225,7 +330,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +362,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -406,7 +519,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -451,6 +564,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -525,7 +647,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>211194</xdr:colOff>
+      <xdr:colOff>27044</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>149311</xdr:rowOff>
     </xdr:to>
@@ -569,7 +691,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>364372</xdr:colOff>
+      <xdr:colOff>180222</xdr:colOff>
       <xdr:row>65</xdr:row>
       <xdr:rowOff>227901</xdr:rowOff>
     </xdr:to>
@@ -613,7 +735,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>341468</xdr:colOff>
+      <xdr:colOff>157318</xdr:colOff>
       <xdr:row>97</xdr:row>
       <xdr:rowOff>60428</xdr:rowOff>
     </xdr:to>
@@ -911,6 +1033,236 @@
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>に返ってきたコードを使用します。</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>9410</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>108426</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09EF2E55-D5A9-4112-966B-B7992CEABFCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="26974800"/>
+          <a:ext cx="8118360" cy="1708626"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>515251</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>19308</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21B2C43A-F4A0-040D-9CCE-7733C7CA10EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="29718000"/>
+          <a:ext cx="6458851" cy="1848108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="フレーム 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61303632-9790-2481-C68A-9A718A3C46E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1130300" y="29883100"/>
+          <a:ext cx="5975350" cy="336550"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 0"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="フレーム 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94B6127B-1A06-4781-B45D-190EC37C17C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1104900" y="30359350"/>
+          <a:ext cx="5988050" cy="336550"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 0"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1216,8 +1568,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171FAAD8-FD6C-481B-9862-C6787CEA2737}">
-  <dimension ref="A1:S124"/>
+  <dimension ref="A1:S141"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="13" max="13" width="11.08203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
@@ -1277,60 +1632,60 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="13"/>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="13"/>
-      <c r="K101" s="13"/>
-      <c r="L101" s="13"/>
-      <c r="M101" s="13"/>
-      <c r="N101" s="13"/>
-      <c r="O101" s="13"/>
-      <c r="P101" s="13"/>
-      <c r="Q101" s="13"/>
-      <c r="R101" s="13"/>
-      <c r="S101" s="14"/>
+      <c r="B101" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="16"/>
+      <c r="H101" s="16"/>
+      <c r="I101" s="16"/>
+      <c r="J101" s="16"/>
+      <c r="K101" s="16"/>
+      <c r="L101" s="16"/>
+      <c r="M101" s="16"/>
+      <c r="N101" s="16"/>
+      <c r="O101" s="16"/>
+      <c r="P101" s="16"/>
+      <c r="Q101" s="16"/>
+      <c r="R101" s="16"/>
+      <c r="S101" s="17"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" t="str">
         <f>RIGHT(LEFT(B101,FIND("&amp;scope",B101)-1),LEN(LEFT(B101,FIND("&amp;scope",B101)-1))-FIND("code=",LEFT(B101,FIND("&amp;scope",B101)-1))-4)</f>
-        <v>4/0ATX87lNdBy2sjOWjjq5VPylsN9fm4OMmlqyY9qrRjn14Dpx3TMKn-P4C5e9a3amu6_jgwQ</v>
+        <v>4/0ATX87lPXgQMsyNd5hcMYeNlwFU5igZ77FB8fUD1UVsVA33oWE3gmpg_QTrqA34mQGpc71g</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
@@ -1345,8 +1700,9 @@
       <c r="M110" s="5"/>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="6" t="s">
-        <v>17</v>
+      <c r="B111" s="6" t="str">
+        <f>"  --data-urlencode ""code=" &amp; B104 &amp; """ ^"</f>
+        <v xml:space="preserve">  --data-urlencode "code=4/0ATX87lPXgQMsyNd5hcMYeNlwFU5igZ77FB8fUD1UVsVA33oWE3gmpg_QTrqA34mQGpc71g" ^</v>
       </c>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
@@ -1360,12 +1716,12 @@
       <c r="L111" s="7"/>
       <c r="M111" s="8"/>
       <c r="N111" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
@@ -1379,12 +1735,12 @@
       <c r="L112" s="7"/>
       <c r="M112" s="8"/>
       <c r="N112" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
@@ -1398,12 +1754,12 @@
       <c r="L113" s="7"/>
       <c r="M113" s="8"/>
       <c r="N113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
@@ -1419,7 +1775,7 @@
     </row>
     <row r="115" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" s="9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="10"/>
@@ -1435,106 +1791,23 @@
     </row>
     <row r="117" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B129" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B119" s="3" t="str">
-        <f>"curl -X POST ""https://oauth2.googleapis.com/token"" ^"</f>
-        <v>curl -X POST "https://oauth2.googleapis.com/token" ^</v>
-      </c>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
-      <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
-      <c r="J119" s="4"/>
-      <c r="K119" s="4"/>
-      <c r="L119" s="4"/>
-      <c r="M119" s="5"/>
-    </row>
-    <row r="120" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="6" t="str">
-        <f>"  --data-urlencode ""code=" &amp; B104 &amp; """ ^"</f>
-        <v xml:space="preserve">  --data-urlencode "code=4/0ATX87lNdBy2sjOWjjq5VPylsN9fm4OMmlqyY9qrRjn14Dpx3TMKn-P4C5e9a3amu6_jgwQ" ^</v>
-      </c>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="8"/>
-    </row>
-    <row r="121" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7"/>
-      <c r="J121" s="7"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
-      <c r="M121" s="8"/>
-    </row>
-    <row r="122" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B122" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="7"/>
-      <c r="I122" s="7"/>
-      <c r="J122" s="7"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
-      <c r="M122" s="8"/>
-    </row>
-    <row r="123" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="7"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="7"/>
-      <c r="M123" s="8"/>
-    </row>
-    <row r="124" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="9" t="s">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B141" t="s">
         <v>22</v>
       </c>
-      <c r="C124" s="10"/>
-      <c r="D124" s="10"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="10"/>
-      <c r="G124" s="10"/>
-      <c r="H124" s="10"/>
-      <c r="I124" s="10"/>
-      <c r="J124" s="10"/>
-      <c r="K124" s="10"/>
-      <c r="L124" s="10"/>
-      <c r="M124" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
